--- a/Result/profitability/1762.xlsx
+++ b/Result/profitability/1762.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3425</v>
+        <v>-0.235</v>
       </c>
       <c r="N2" t="n">
-        <v>9.986250000000002</v>
+        <v>11.57</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.75</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.11</v>
+        <v>-0.01500000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>11.63875</v>
+        <v>13.25875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.89</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1275</v>
+        <v>0.205</v>
       </c>
       <c r="N4" t="n">
-        <v>14.36875</v>
+        <v>15.18625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1825</v>
+        <v>0.4275</v>
       </c>
       <c r="N5" t="n">
-        <v>16.14</v>
+        <v>19.8175</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,13 +1137,13 @@
         <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0.38375</v>
+        <v>0.57375</v>
       </c>
       <c r="N6" t="n">
-        <v>20.215</v>
+        <v>25.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.85</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5862499999999999</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>27.4425</v>
+        <v>42.03375</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,13 +1282,13 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.40000000000001</v>
@@ -1391,10 +1391,10 @@
         <v>0.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.97</v>
+        <v>0.85875</v>
       </c>
       <c r="N8" t="n">
-        <v>41.645</v>
+        <v>41.1725</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.6</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8400000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="N9" t="n">
         <v>41.38</v>
@@ -1645,7 +1645,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.91</v>
+        <v>0.9099999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>42.25625</v>
@@ -9576,6 +9576,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1762</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>305</v>
+      </c>
+      <c r="D73" t="n">
+        <v>189</v>
+      </c>
+      <c r="E73" t="n">
+        <v>116</v>
+      </c>
+      <c r="F73" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="G73" t="n">
+        <v>35</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>11.55%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>13</v>
+      </c>
+      <c r="J73" t="n">
+        <v>49</v>
+      </c>
+      <c r="K73" t="n">
+        <v>42</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-0.265</v>
+      </c>
+      <c r="N73" t="n">
+        <v>10.6075</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-0.8899999999999999</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-0.5426829268292683</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>-3.780000000000001</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>-0.09066922523386911</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-1.619834710743802</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>29.41999999999999</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>3.465253239104829</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
